--- a/teacher_forms/001_listening_quiz--teacher_forms.xlsx
+++ b/teacher_forms/001_listening_quiz--teacher_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Page 1</t>
+          <t>Introduction</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,14 +548,10 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Listening Quiz</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Create interactive listening tests</t>
-        </is>
-      </c>
+          <t>Interactive Listening Test</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>no</t>
@@ -598,10 +594,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Multiple Choice Question</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Select the correct option</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -621,10 +621,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Short Answer</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Short Answer Question</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Enter your answer</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -644,10 +648,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Audio</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Audio File Upload</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Upload a audio file</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -657,7 +665,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -667,10 +675,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>File Upload</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Date of Listening</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Enter the date of the listening test</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -680,7 +692,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -690,10 +702,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Time of Listening</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Enter the time of the listening test</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -703,7 +719,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -713,10 +729,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Time</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Contact Information</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Enter your email address</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -726,7 +746,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -736,10 +756,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Additional Notes</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Add any additional comments</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -749,7 +773,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -759,10 +783,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Select One Question</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Select the correct option</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -772,7 +800,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -782,12 +810,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>Select Multiple Question</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Add a note to the form</t>
+          <t>Select multiple options</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -799,7 +827,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -809,10 +837,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Select One</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Decimal Number Question</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Enter a decimal number</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>no</t>
@@ -822,7 +854,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -832,12 +864,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Select Multiple</t>
+          <t>Integer Number Question</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Select multiple options</t>
+          <t>Enter an integer number</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -859,10 +891,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Decimal Number</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Text Field</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Enter any text</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>no</t>
@@ -872,7 +908,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -882,10 +918,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Integer Number</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Time Question</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Enter a time</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>no</t>
@@ -895,7 +935,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -905,10 +945,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Date Question</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Enter a date</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>no</t>
@@ -918,7 +962,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -928,174 +972,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Time</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>Submit Question</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Enter your response</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>page_19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>page_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Select One</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>page_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Select Multiple</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>page_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Decimal Number</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>page_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Integer Number</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>page_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>page_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Submit</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1110,7 +997,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1206,41 +1093,41 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>page_13_choices</t>
+          <t>page_11_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>page_13_choices</t>
+          <t>page_11_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>page_14_choices</t>
+          <t>page_12_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1257,7 +1144,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>page_14_choices</t>
+          <t>page_12_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1274,7 +1161,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>page_14_choices</t>
+          <t>page_12_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1291,7 +1178,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>page_14_choices</t>
+          <t>page_12_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1300,108 +1187,6 @@
         </is>
       </c>
       <c r="C11" t="inlineStr">
-        <is>
-          <t>Option D</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>page_20_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>page_20_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>page_21_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>option_a</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Option A</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>page_21_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>option_b</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>page_21_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>option_c</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Option C</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>page_21_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>option_d</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
         <is>
           <t>Option D</t>
         </is>
